--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:51</t>
+    <t xml:space="preserve">2026-08-17 22:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 22:11</t>
+    <t xml:space="preserve">2026-09-01 17:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:49</t>
+    <t xml:space="preserve">2026-09-06 22:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
